--- a/resources/interaction.xlsx
+++ b/resources/interaction.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="740" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Interaction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="InteractionConv" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="InteractionConvOption" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interaction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractionConv" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InteractionConvOption" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.875" customWidth="1" style="21" min="1" max="1"/>
@@ -2821,15 +2821,15 @@
       <c r="P70" s="28" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="26" t="n"/>
+      <c r="A71" s="26" t="n">
+        <v>10071</v>
+      </c>
       <c r="B71" s="26" t="n"/>
-      <c r="C71" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="D71" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E71" s="27" t="n"/>
+      <c r="C71" s="26" t="n"/>
+      <c r="D71" s="26" t="n"/>
+      <c r="E71" s="27" t="n">
+        <v>3006</v>
+      </c>
       <c r="F71" s="28" t="n"/>
       <c r="G71" s="29" t="n"/>
       <c r="H71" s="28" t="n"/>
@@ -2838,9 +2838,33 @@
       <c r="K71" s="28" t="n"/>
       <c r="L71" s="28" t="n"/>
       <c r="M71" s="28" t="n"/>
-      <c r="N71" s="28" t="n"/>
+      <c r="N71" s="28" t="n">
+        <v>10071</v>
+      </c>
       <c r="O71" s="29" t="n"/>
       <c r="P71" s="28" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="26" t="n"/>
+      <c r="B72" s="26" t="n"/>
+      <c r="C72" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="27" t="n"/>
+      <c r="F72" s="28" t="n"/>
+      <c r="G72" s="29" t="n"/>
+      <c r="H72" s="28" t="n"/>
+      <c r="I72" s="30" t="n"/>
+      <c r="J72" s="30" t="n"/>
+      <c r="K72" s="28" t="n"/>
+      <c r="L72" s="28" t="n"/>
+      <c r="M72" s="28" t="n"/>
+      <c r="N72" s="28" t="n"/>
+      <c r="O72" s="29" t="n"/>
+      <c r="P72" s="28" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
@@ -2873,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="12" min="1" max="1"/>
@@ -3503,6 +3527,24 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>10071</v>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>，对话内容为欢迎来到铁匠铺，我可以帮你锻造装备</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>10071</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>10072</v>
+      </c>
+      <c r="F31" s="0" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 C1:C4 E3:E4 G3:G4 I3:I4">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
@@ -3518,7 +3560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.125" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
@@ -4250,6 +4292,36 @@
       </c>
       <c r="F41" s="0" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>10071</v>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>好的，我要锻造</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="0" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>10072</v>
+      </c>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>10071</v>
+      </c>
+      <c r="F43" s="0" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 C1:E4">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>

--- a/resources/interaction.xlsx
+++ b/resources/interaction.xlsx
@@ -976,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.875" customWidth="1" style="21" min="1" max="1"/>
@@ -1175,53 +1175,49 @@
       <c r="P3" s="16" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="8">
-      <c r="A4" s="23" t="n">
-        <v>10001</v>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>擂台npc</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="n">
-        <v>102</v>
-      </c>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
-      <c r="I4" s="24" t="n"/>
-      <c r="J4" s="24" t="n"/>
-      <c r="K4" s="24" t="n"/>
-      <c r="L4" s="24" t="n"/>
-      <c r="M4" s="24" t="n"/>
-      <c r="N4" s="24" t="n"/>
+      <c r="A4" s="10" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="15" t="n">
+        <v>3006</v>
+      </c>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="n">
+        <v>3006</v>
+      </c>
       <c r="O4" s="18" t="n"/>
       <c r="P4" s="16" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
       <c r="A5" s="21" t="n">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>奖励npc</t>
+          <t>擂台npc</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n">
-        <v>3002</v>
-      </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n">
-        <v>10006</v>
-      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n"/>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
@@ -1229,26 +1225,28 @@
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="28" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="21" t="n">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>传送npc</t>
+          <t>奖励npc</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="G6" s="11" t="n">
+        <v>10006</v>
+      </c>
+      <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
@@ -1258,7 +1256,7 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="21" t="n">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1273,7 +1271,7 @@
       <c r="F7" s="11" t="n"/>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n">
-        <v>10001</v>
+        <v>0</v>
       </c>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
@@ -1284,7 +1282,7 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="21" t="n">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
@@ -1294,17 +1292,15 @@
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n">
+      <c r="H8" s="11" t="n">
         <v>10001</v>
       </c>
-      <c r="J8" s="11" t="n">
-        <v>50001</v>
-      </c>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="n"/>
       <c r="M8" s="11" t="n"/>
@@ -1312,7 +1308,7 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="21" t="n">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -1322,66 +1318,68 @@
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n">
+      <c r="I9" s="11" t="n">
         <v>10001</v>
       </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>80, 0, 59</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="11" t="n">
+        <v>50001</v>
+      </c>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="21" t="n">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>获得洞府</t>
+          <t>传送npc</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n">
-        <v>4003</v>
+        <v>3005</v>
       </c>
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n"/>
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="K10" s="11" t="n">
+        <v>10001</v>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>80, 0, 59</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" s="11" t="n"/>
-      <c r="O10" s="12" t="n">
-        <v>30004</v>
-      </c>
+      <c r="O10" s="12" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="21" t="n">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>添加分身</t>
+          <t>获得洞府</t>
         </is>
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n"/>
@@ -1392,21 +1390,23 @@
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
-      <c r="O11" s="12" t="n"/>
+      <c r="O11" s="12" t="n">
+        <v>30004</v>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="21" t="n">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>切换门派</t>
+          <t>添加分身</t>
         </is>
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
@@ -1417,26 +1417,23 @@
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
+      <c r="O12" s="12" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="21" t="n">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>任务战斗测试</t>
+          <t>切换门派</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>25001001</v>
-      </c>
+      <c r="E13" s="11" t="n">
+        <v>4005</v>
+      </c>
+      <c r="F13" s="11" t="n"/>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
       <c r="I13" s="11" t="n"/>
@@ -1448,7 +1445,7 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" s="8">
       <c r="A14" s="21" t="n">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
@@ -1476,20 +1473,22 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="21" t="n">
-        <v>10012</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>练气木桩</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="11" t="n">
-        <v>3001</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>25001002</v>
+        <v>10011</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>任务战斗测试</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>25001001</v>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
@@ -1502,11 +1501,11 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="21" t="n">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>筑基木桩</t>
+          <t>练气木桩</t>
         </is>
       </c>
       <c r="C16" s="25" t="n"/>
@@ -1515,7 +1514,7 @@
         <v>3001</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>25001003</v>
+        <v>25001002</v>
       </c>
       <c r="G16" s="11" t="n"/>
       <c r="H16" s="11" t="n"/>
@@ -1528,11 +1527,11 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" s="8">
       <c r="A17" s="21" t="n">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>金丹木桩</t>
+          <t>筑基木桩</t>
         </is>
       </c>
       <c r="C17" s="25" t="n"/>
@@ -1541,7 +1540,7 @@
         <v>3001</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25001004</v>
+        <v>25001003</v>
       </c>
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
@@ -1554,11 +1553,11 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" s="8">
       <c r="A18" s="21" t="n">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>元婴木桩</t>
+          <t>金丹木桩</t>
         </is>
       </c>
       <c r="C18" s="25" t="n"/>
@@ -1567,7 +1566,7 @@
         <v>3001</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>25001005</v>
+        <v>25001004</v>
       </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
@@ -1580,11 +1579,11 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" s="8">
       <c r="A19" s="21" t="n">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>化神木桩</t>
+          <t>元婴木桩</t>
         </is>
       </c>
       <c r="C19" s="25" t="n"/>
@@ -1593,7 +1592,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>25001006</v>
+        <v>25001005</v>
       </c>
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="n"/>
@@ -1606,19 +1605,21 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" s="8">
       <c r="A20" s="21" t="n">
-        <v>10017</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>获取洞府</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
+        <v>10016</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>化神木桩</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
       <c r="E20" s="11" t="n">
-        <v>4003</v>
-      </c>
-      <c r="F20" s="11" t="n"/>
+        <v>3001</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>25001006</v>
+      </c>
       <c r="G20" s="11" t="n"/>
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="n"/>
@@ -1627,23 +1628,21 @@
       <c r="L20" s="11" t="n"/>
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="11" t="n"/>
-      <c r="O20" s="12" t="n">
-        <v>30004</v>
-      </c>
+      <c r="O20" s="12" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="8">
       <c r="A21" s="21" t="n">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>获取分身</t>
+          <t>获取洞府</t>
         </is>
       </c>
       <c r="C21" s="22" t="n"/>
       <c r="D21" s="22" t="n"/>
       <c r="E21" s="11" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="11" t="n"/>
@@ -1654,21 +1653,23 @@
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
-      <c r="O21" s="12" t="n"/>
+      <c r="O21" s="12" t="n">
+        <v>30004</v>
+      </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="8">
       <c r="A22" s="21" t="n">
-        <v>10019</v>
+        <v>10018</v>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>更换门派</t>
+          <t>获取分身</t>
         </is>
       </c>
       <c r="C22" s="22" t="n"/>
       <c r="D22" s="22" t="n"/>
       <c r="E22" s="11" t="n">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="11" t="n"/>
@@ -1679,26 +1680,23 @@
       <c r="L22" s="11" t="n"/>
       <c r="M22" s="11" t="n"/>
       <c r="N22" s="11" t="n"/>
+      <c r="O22" s="12" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="8">
       <c r="A23" s="21" t="n">
-        <v>10020</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>100011000</v>
-      </c>
+        <v>10019</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>更换门派</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="11" t="n">
+        <v>4005</v>
+      </c>
+      <c r="F23" s="11" t="n"/>
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="11" t="n"/>
@@ -1710,11 +1708,11 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" s="8">
       <c r="A24" s="21" t="n">
-        <v>10021</v>
+        <v>10020</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>中级灵脉</t>
+          <t>低级灵脉</t>
         </is>
       </c>
       <c r="C24" s="11" t="n"/>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>100011001</v>
+        <v>100011000</v>
       </c>
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="n"/>
@@ -1738,11 +1736,11 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="8">
       <c r="A25" s="21" t="n">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>高级灵脉</t>
+          <t>中级灵脉</t>
         </is>
       </c>
       <c r="C25" s="11" t="n"/>
@@ -1753,7 +1751,7 @@
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>100011002</v>
+        <v>100011001</v>
       </c>
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="n"/>
@@ -1766,19 +1764,23 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" s="8">
       <c r="A26" s="21" t="n">
-        <v>10023</v>
+        <v>10022</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>洞府出口</t>
+          <t>高级灵脉</t>
         </is>
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n">
-        <v>4001</v>
-      </c>
-      <c r="F26" s="11" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>100011002</v>
+      </c>
       <c r="G26" s="11" t="n"/>
       <c r="H26" s="11" t="n"/>
       <c r="I26" s="11" t="n"/>
@@ -1790,39 +1792,31 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="8">
       <c r="A27" s="21" t="n">
-        <v>10024</v>
+        <v>10023</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>洞府传送阵</t>
+          <t>洞府出口</t>
         </is>
       </c>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n">
-        <v>3005</v>
+        <v>4001</v>
       </c>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="11" t="n"/>
       <c r="H27" s="11" t="n"/>
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>74,0,42</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="8">
       <c r="A28" s="21" t="n">
-        <v>10025</v>
+        <v>10024</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
@@ -1844,7 +1838,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>25,-3,36</t>
+          <t>74,0,42</t>
         </is>
       </c>
       <c r="M28" s="11" t="n">
@@ -1854,47 +1848,51 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" s="8">
       <c r="A29" s="21" t="n">
-        <v>10026</v>
+        <v>10025</v>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>灵兽抽奖</t>
+          <t>洞府传送阵</t>
         </is>
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="11" t="n">
-        <v>4002</v>
+        <v>3005</v>
       </c>
       <c r="F29" s="11" t="n"/>
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>25,-3,36</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" s="11" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="8">
       <c r="A30" s="21" t="n">
-        <v>10027</v>
+        <v>10026</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>低级灵脉</t>
+          <t>灵兽抽奖</t>
         </is>
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>100011000</v>
-      </c>
+      <c r="E30" s="11" t="n">
+        <v>4002</v>
+      </c>
+      <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="11" t="n"/>
@@ -1906,7 +1904,7 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="8">
       <c r="A31" s="21" t="n">
-        <v>10028</v>
+        <v>10027</v>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
@@ -1934,19 +1932,23 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" s="8">
       <c r="A32" s="21" t="n">
-        <v>10029</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>获取洞府</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="11" t="n">
-        <v>4003</v>
-      </c>
-      <c r="F32" s="11" t="n"/>
+        <v>10028</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>100011000</v>
+      </c>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
       <c r="I32" s="11" t="n"/>
@@ -1955,29 +1957,23 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
-      <c r="O32" s="12" t="n">
-        <v>30004</v>
-      </c>
+      <c r="O32" s="12" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="8">
       <c r="A33" s="21" t="n">
-        <v>10030</v>
+        <v>10029</v>
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>游荡怪物</t>
+          <t>获取洞府</t>
         </is>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>102</v>
-      </c>
+      <c r="E33" s="11" t="n">
+        <v>4003</v>
+      </c>
+      <c r="F33" s="11" t="n"/>
       <c r="G33" s="11" t="n"/>
       <c r="H33" s="11" t="n"/>
       <c r="I33" s="11" t="n"/>
@@ -1986,19 +1982,21 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="11" t="n"/>
       <c r="N33" s="11" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="O33" s="12" t="n">
+        <v>30004</v>
+      </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="8">
       <c r="A34" s="21" t="n">
-        <v>10031</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
+        <v>10030</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>游荡怪物</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
           <t>3001</t>
@@ -2015,22 +2013,27 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
+      <c r="O34" s="12" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="8">
       <c r="A35" s="21" t="n">
-        <v>10032</v>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>帮派攻城战传送</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="11" t="n">
-        <v>4006</v>
-      </c>
-      <c r="F35" s="11" t="n"/>
+        <v>10031</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>102</v>
+      </c>
       <c r="G35" s="11" t="n"/>
       <c r="H35" s="11" t="n"/>
       <c r="I35" s="11" t="n"/>
@@ -2042,17 +2045,17 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" s="8">
       <c r="A36" s="21" t="n">
-        <v>10033</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>测试对话</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
+        <v>10032</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>帮派攻城战传送</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
       <c r="E36" s="11" t="n">
-        <v>3006</v>
+        <v>4006</v>
       </c>
       <c r="F36" s="11" t="n"/>
       <c r="G36" s="11" t="n"/>
@@ -2062,17 +2065,15 @@
       <c r="K36" s="11" t="n"/>
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="11" t="n"/>
-      <c r="N36" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N36" s="11" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="8">
       <c r="A37" s="21" t="n">
-        <v>10034</v>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>帮派青龙堂总管</t>
+        <v>10033</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>测试对话</t>
         </is>
       </c>
       <c r="C37" s="11" t="n"/>
@@ -2088,17 +2089,17 @@
       <c r="K37" s="11" t="n"/>
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="11" t="n"/>
-      <c r="N37" s="12" t="n">
-        <v>4</v>
+      <c r="N37" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="8">
       <c r="A38" s="21" t="n">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>帮派白虎堂总管</t>
+          <t>帮派青龙堂总管</t>
         </is>
       </c>
       <c r="C38" s="11" t="n"/>
@@ -2115,16 +2116,16 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="11" t="n"/>
       <c r="N38" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="8">
       <c r="A39" s="21" t="n">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>帮派朱雀堂总管</t>
+          <t>帮派白虎堂总管</t>
         </is>
       </c>
       <c r="C39" s="11" t="n"/>
@@ -2141,16 +2142,16 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="8">
       <c r="A40" s="21" t="n">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>帮派玄武堂总管</t>
+          <t>帮派朱雀堂总管</t>
         </is>
       </c>
       <c r="C40" s="11" t="n"/>
@@ -2167,102 +2168,112 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="11" t="n"/>
       <c r="N40" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="8">
       <c r="A41" s="21" t="n">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>兽栏门口NPC</t>
-        </is>
-      </c>
+          <t>帮派玄武堂总管</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
       <c r="E41" s="11" t="n">
         <v>3006</v>
       </c>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
       <c r="N41" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="8">
       <c r="A42" s="21" t="n">
-        <v>10039</v>
+        <v>10038</v>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>灵阁门口NPC</t>
+          <t>兽栏门口NPC</t>
         </is>
       </c>
       <c r="E42" s="11" t="n">
         <v>3006</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="8">
       <c r="A43" s="21" t="n">
-        <v>10040</v>
+        <v>10039</v>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>金库门口NPC</t>
+          <t>灵阁门口NPC</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
         <v>3006</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="8">
       <c r="A44" s="21" t="n">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>书院门口NPC</t>
+          <t>金库门口NPC</t>
         </is>
       </c>
       <c r="E44" s="11" t="n">
         <v>3006</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="8">
       <c r="A45" s="21" t="n">
-        <v>10042</v>
+        <v>10041</v>
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>商店门口NPC</t>
+          <t>书院门口NPC</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
         <v>3006</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="8">
       <c r="A46" s="21" t="n">
-        <v>10043</v>
+        <v>10042</v>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>攻城战传送（战场内）</t>
+          <t>商店门口NPC</t>
         </is>
       </c>
       <c r="C46" s="22" t="n"/>
       <c r="D46" s="22" t="n"/>
       <c r="E46" s="11" t="n">
-        <v>4007</v>
+        <v>3006</v>
       </c>
       <c r="F46" s="11" t="n"/>
       <c r="G46" s="11" t="n"/>
@@ -2272,23 +2283,23 @@
       <c r="K46" s="11" t="n"/>
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="11" t="n"/>
-      <c r="N46" s="11" t="n"/>
+      <c r="N46" s="12" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="8">
       <c r="A47" s="21" t="n">
-        <v>10044</v>
+        <v>10043</v>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>攻城战城门/大营门</t>
+          <t>攻城战传送（战场内）</t>
         </is>
       </c>
       <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n">
-        <v>10</v>
-      </c>
+      <c r="D47" s="22" t="n"/>
       <c r="E47" s="11" t="n">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="11" t="n"/>
@@ -2302,11 +2313,11 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" s="8">
       <c r="A48" s="21" t="n">
-        <v>10046</v>
+        <v>10044</v>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>攻城战主府</t>
+          <t>攻城战城门/大营门</t>
         </is>
       </c>
       <c r="C48" s="22" t="n"/>
@@ -2314,7 +2325,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="F48" s="11" t="n"/>
       <c r="G48" s="11" t="n"/>
@@ -2328,17 +2339,19 @@
     </row>
     <row r="49" ht="17.25" customHeight="1" s="8">
       <c r="A49" s="21" t="n">
-        <v>10047</v>
+        <v>10046</v>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>攻城战图腾</t>
+          <t>攻城战主府</t>
         </is>
       </c>
       <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
+      <c r="D49" s="22" t="n">
+        <v>10</v>
+      </c>
       <c r="E49" s="11" t="n">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="F49" s="11" t="n"/>
       <c r="G49" s="11" t="n"/>
@@ -2352,17 +2365,17 @@
     </row>
     <row r="50" ht="16.5" customHeight="1" s="8">
       <c r="A50" s="21" t="n">
-        <v>10051</v>
+        <v>10047</v>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>攻城巨兽</t>
+          <t>攻城战图腾</t>
         </is>
       </c>
       <c r="C50" s="22" t="n"/>
       <c r="D50" s="22" t="n"/>
       <c r="E50" s="11" t="n">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="F50" s="11" t="n"/>
       <c r="G50" s="11" t="n"/>
@@ -2376,17 +2389,17 @@
     </row>
     <row r="51" ht="16.5" customHeight="1" s="8">
       <c r="A51" s="21" t="n">
-        <v>10052</v>
+        <v>10051</v>
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>胜利宝箱</t>
+          <t>攻城巨兽</t>
         </is>
       </c>
       <c r="C51" s="22" t="n"/>
       <c r="D51" s="22" t="n"/>
       <c r="E51" s="11" t="n">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="F51" s="11" t="n"/>
       <c r="G51" s="11" t="n"/>
@@ -2400,17 +2413,17 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" s="8">
       <c r="A52" s="21" t="n">
-        <v>10053</v>
+        <v>10052</v>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>庆贺宝箱</t>
+          <t>胜利宝箱</t>
         </is>
       </c>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="22" t="n"/>
       <c r="E52" s="11" t="n">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="F52" s="11" t="n"/>
       <c r="G52" s="11" t="n"/>
@@ -2424,17 +2437,17 @@
     </row>
     <row r="53" ht="16.5" customHeight="1" s="8">
       <c r="A53" s="21" t="n">
-        <v>10054</v>
+        <v>10053</v>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>聚义厅门口NPC</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
+          <t>庆贺宝箱</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
       <c r="E53" s="11" t="n">
-        <v>3006</v>
+        <v>4013</v>
       </c>
       <c r="F53" s="11" t="n"/>
       <c r="G53" s="11" t="n"/>
@@ -2444,122 +2457,133 @@
       <c r="K53" s="11" t="n"/>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="11" t="n"/>
-      <c r="N53" s="12" t="n">
-        <v>13</v>
-      </c>
+      <c r="N53" s="11" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="8">
       <c r="A54" s="21" t="n">
-        <v>10055</v>
+        <v>10054</v>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>主城交互</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>7</v>
-      </c>
+          <t>聚义厅门口NPC</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
       <c r="E54" s="11" t="n">
-        <v>4014</v>
-      </c>
-      <c r="N54" s="12" t="n"/>
+        <v>3006</v>
+      </c>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="11" t="n"/>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="12" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="8">
       <c r="A55" s="21" t="n">
-        <v>10056</v>
+        <v>10055</v>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>内城城门交互</t>
+          <t>主城交互</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>4015</v>
-      </c>
+        <v>4014</v>
+      </c>
+      <c r="N55" s="12" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="8">
       <c r="A56" s="21" t="n">
-        <v>10057</v>
+        <v>10056</v>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>卫城交互</t>
+          <t>内城城门交互</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D56" s="12" t="n">
         <v>6</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>4014</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="8">
       <c r="A57" s="21" t="n">
-        <v>10058</v>
+        <v>10057</v>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>切换心法</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
+          <t>卫城交互</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="E57" s="11" t="n">
-        <v>4016</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="8">
       <c r="A58" s="21" t="n">
-        <v>10059</v>
+        <v>10058</v>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>创建帮派</t>
-        </is>
-      </c>
+          <t>切换心法</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
       <c r="E58" s="11" t="n">
-        <v>4017</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="8">
       <c r="A59" s="21" t="n">
-        <v>10060</v>
+        <v>10059</v>
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>占领城池</t>
+          <t>创建帮派</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>4018</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="8">
       <c r="A60" s="21" t="n">
-        <v>10061</v>
+        <v>10060</v>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>S1_world01洞府例子</t>
+          <t>占领城池</t>
         </is>
       </c>
       <c r="C60" s="22" t="n"/>
       <c r="D60" s="22" t="n"/>
       <c r="E60" s="11" t="n">
-        <v>4003</v>
+        <v>4018</v>
       </c>
       <c r="F60" s="11" t="n"/>
       <c r="G60" s="11" t="n"/>
@@ -2570,18 +2594,22 @@
       <c r="L60" s="11" t="n"/>
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
-      <c r="O60" s="12" t="n">
-        <v>30005</v>
-      </c>
+      <c r="O60" s="12" t="n"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="8">
       <c r="A61" s="21" t="n">
-        <v>25083003</v>
-      </c>
-      <c r="B61" s="22" t="n"/>
+        <v>10061</v>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>S1_world01洞府例子</t>
+        </is>
+      </c>
       <c r="C61" s="22" t="n"/>
       <c r="D61" s="22" t="n"/>
-      <c r="E61" s="11" t="n"/>
+      <c r="E61" s="11" t="n">
+        <v>4003</v>
+      </c>
       <c r="F61" s="11" t="n"/>
       <c r="G61" s="11" t="n"/>
       <c r="H61" s="11" t="n"/>
@@ -2591,29 +2619,79 @@
       <c r="L61" s="11" t="n"/>
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
-      <c r="O61" s="12" t="n"/>
+      <c r="O61" s="12" t="n">
+        <v>30005</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="n"/>
-      <c r="B62" s="26" t="n"/>
-      <c r="C62" s="26" t="n">
+      <c r="A62" s="21" t="n">
+        <v>25083003</v>
+      </c>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="11" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="11" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="11" t="n"/>
+      <c r="O62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="n">
+        <v>25083005</v>
+      </c>
+      <c r="B63" s="26" t="n"/>
+      <c r="C63" s="26" t="n"/>
+      <c r="D63" s="26" t="n"/>
+      <c r="E63" s="27" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F63" s="28" t="n">
+        <v>25083002</v>
+      </c>
+      <c r="G63" s="29" t="n">
+        <v>100831</v>
+      </c>
+      <c r="H63" s="28" t="n"/>
+      <c r="I63" s="30" t="n"/>
+      <c r="J63" s="30" t="n"/>
+      <c r="K63" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="28" t="n"/>
+      <c r="M63" s="28" t="n"/>
+      <c r="N63" s="28" t="n"/>
+      <c r="O63" s="29" t="n"/>
+      <c r="P63" s="28" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="26" t="n"/>
+      <c r="B64" s="26" t="n"/>
+      <c r="C64" s="26" t="n">
         <v>30</v>
       </c>
-      <c r="D62" s="26" t="n">
+      <c r="D64" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="E62" s="27" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="29" t="n"/>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="30" t="n"/>
-      <c r="J62" s="30" t="n"/>
-      <c r="K62" s="28" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="28" t="n"/>
-      <c r="N62" s="28" t="n"/>
-      <c r="O62" s="29" t="n"/>
-      <c r="P62" s="28" t="n"/>
+      <c r="E64" s="27" t="n"/>
+      <c r="F64" s="28" t="n"/>
+      <c r="G64" s="29" t="n"/>
+      <c r="H64" s="28" t="n"/>
+      <c r="I64" s="30" t="n"/>
+      <c r="J64" s="30" t="n"/>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="28" t="n"/>
+      <c r="M64" s="28" t="n"/>
+      <c r="N64" s="28" t="n"/>
+      <c r="O64" s="29" t="n"/>
+      <c r="P64" s="28" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
@@ -2646,7 +2724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="12" min="1" max="1"/>
@@ -2781,7 +2859,7 @@
           <t>测试对话</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>对话1</t>
         </is>
@@ -2805,7 +2883,7 @@
           <t>测试对话</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>对话2</t>
         </is>
@@ -2911,12 +2989,12 @@
       <c r="A12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>兽栏门口NPC对话</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>兽栏是帮派攻城巨兽的栖息之所，升级兽栏可以提升攻城巨兽的等级上限。</t>
         </is>
@@ -2929,12 +3007,12 @@
       <c r="A13" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>灵阁门口NPC对话</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>灵阁升级可以增加帮派人数上限。</t>
         </is>
@@ -2947,12 +3025,12 @@
       <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>金库门口NPC对话</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>帮派金库升级后可以增加帮派任务获得的帮派分红，同时可以提升帮派资金上限。</t>
         </is>
@@ -2965,12 +3043,12 @@
       <c r="A15" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>书院门口NPC对话</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>书院是帮派技能研究的场所，可以提升帮派技能等级的上限。</t>
         </is>
@@ -2986,12 +3064,12 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>商店门口NPC对话</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>在我这里可以用帮贡购买好东西哦。（暂未开放）</t>
         </is>
@@ -3007,18 +3085,46 @@
       <c r="A17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>聚义厅门口NPC对话</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>聚义厅等级决定了其他帮派建筑的等级上限。</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>要打造装备吗？</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>25083004</v>
+      </c>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>对话结束</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>25083004</v>
       </c>
     </row>
   </sheetData>
@@ -3036,7 +3142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11.125" bestFit="1" customWidth="1" style="12" min="1" max="1"/>
@@ -3134,12 +3240,12 @@
           <t>测试对话</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>打开对话2</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
+      <c r="D5" s="22" t="n"/>
       <c r="E5" s="12" t="n">
         <v>1</v>
       </c>
@@ -3156,12 +3262,12 @@
           <t>测试对话</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>打开对话3</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n"/>
+      <c r="D6" s="22" t="n"/>
       <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
@@ -3281,17 +3387,17 @@
       <c r="A13" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>打开升级兽栏界面</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>升级兽栏</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n"/>
+      <c r="D13" s="22" t="n"/>
       <c r="E13" s="12" t="n">
         <v>1005</v>
       </c>
@@ -3300,17 +3406,17 @@
       <c r="A14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>打开升级灵阁界面</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>升级灵阁</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n"/>
+      <c r="D14" s="22" t="n"/>
       <c r="E14" s="12" t="n">
         <v>1006</v>
       </c>
@@ -3319,17 +3425,17 @@
       <c r="A15" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>打开升级金库界面</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>升级金库</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n"/>
+      <c r="D15" s="22" t="n"/>
       <c r="E15" s="12" t="n">
         <v>1007</v>
       </c>
@@ -3338,17 +3444,17 @@
       <c r="A16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>打开升级书院界面</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>升级书院</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n"/>
+      <c r="D16" s="22" t="n"/>
       <c r="E16" s="12" t="n">
         <v>1008</v>
       </c>
@@ -3357,17 +3463,17 @@
       <c r="A17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>打开升级商店界面</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>升级商店</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n"/>
+      <c r="D17" s="22" t="n"/>
       <c r="E17" s="12" t="n">
         <v>1009</v>
       </c>
@@ -3376,17 +3482,17 @@
       <c r="A18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>打开研究技能界面</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>研究技能</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n"/>
+      <c r="D18" s="22" t="n"/>
       <c r="E18" s="12" t="n">
         <v>1010</v>
       </c>
@@ -3395,17 +3501,17 @@
       <c r="A19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>打开商店界面</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>打开商店</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n"/>
+      <c r="D19" s="22" t="n"/>
       <c r="E19" s="12" t="n">
         <v>1011</v>
       </c>
@@ -3426,6 +3532,40 @@
       </c>
       <c r="E20" s="12" t="n">
         <v>1012</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>3006</v>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>是的</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>25083004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>25083004</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>3006</v>
       </c>
     </row>
   </sheetData>
